--- a/UnityTableTool/Data/道具表.xlsx
+++ b/UnityTableTool/Data/道具表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
   <si>
     <t>table: Item</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>##</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1274,7 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="18.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="4" width="18.625" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1396,18 +1399,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6333333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.8727272727273" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="33" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
@@ -1533,6 +1536,43 @@
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/UnityTableTool/Data/道具表.xlsx
+++ b/UnityTableTool/Data/道具表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game\UnityTools\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t>table: Item</t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>s</t>
-  </si>
-  <si>
-    <t>##</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1271,7 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="18.625" style="1" customWidth="1"/>
+    <col min="1" max="4" width="18.6272727272727" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1403,14 +1400,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6363636363636" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.8727272727273" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="29" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
@@ -1539,41 +1536,18 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UnityTableTool/Data/道具表.xlsx
+++ b/UnityTableTool/Data/道具表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game\UnityTools\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -1271,7 +1271,7 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="18.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="4" width="18.625" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1400,14 +1400,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6333333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.8727272727273" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="33" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>

--- a/UnityTableTool/Data/道具表.xlsx
+++ b/UnityTableTool/Data/道具表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
   <si>
     <t>table: Item</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>slot_num1</t>
   </si>
   <si>
     <t>s</t>
@@ -1271,7 +1274,7 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="18.625" style="1" customWidth="1"/>
+    <col min="1" max="4" width="18.6272727272727" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1400,14 +1403,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6363636363636" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.8727272727273" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="29" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="15" customHeight="1" spans="1:6">
@@ -1532,15 +1535,25 @@
         <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="2"/>
